--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127623385</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92620</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Steresnäset, Steresnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>555087</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6961352</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,6 +1013,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128154348</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Strandåker, Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>555070</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6961372</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>127623385</v>
       </c>
       <c r="B4" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>128154348</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790356</v>
+        <v>96790368</v>
       </c>
       <c r="B2" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555019.6410873156</v>
+        <v>555043</v>
       </c>
       <c r="R2" t="n">
-        <v>6961448.211686283</v>
+        <v>6961477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,21 +752,11 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre sandtallskog, i stig</t>
+          <t>olikåldrig sandtallskog i brink mot sjö</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -805,61 +790,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121310759</v>
+        <v>96790372</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1596</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dragsjömoarna, Jmt</t>
+          <t>Dragsjömon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555014</v>
+        <v>555119</v>
       </c>
       <c r="R3" t="n">
-        <v>6961458</v>
+        <v>6961323</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,64 +878,77 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>130-årig sandtallskog med tunt förnatäcke</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>tunt med väggmossa och lingon på stig</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127623385</v>
+        <v>128518185</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>90674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1596</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Steresnäset, Steresnäset, Jmt</t>
+          <t>Strandåker, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555087</v>
+        <v>555048</v>
       </c>
       <c r="R4" t="n">
-        <v>6961352</v>
+        <v>6961530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +975,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-16</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +995,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128154348</v>
+        <v>96790367</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,48 +1018,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strandåker, Strandåker, Jmt</t>
+          <t>Dragsjömon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555070</v>
+        <v>555050</v>
       </c>
       <c r="R5" t="n">
-        <v>6961372</v>
+        <v>6961492</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,19 +1097,1979 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>olikåldrig sandtallskog i brink mot sjö</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121310745</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92692</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>555118</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6961343</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121310756</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92692</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>555042</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6961450</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128518182</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92692</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1958</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lammticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Albatrellus subrubescens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555052</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6961403</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Erica Hästdahl</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Erica Hästdahl</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96790366</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555051</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6961503</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>olikåldrig sandtallskog i brink mot sjö</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121310749</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555059</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6961397</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121310759</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555014</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6961458</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127623385</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Steresnäset, Steresnäset, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>555087</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6961352</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128369789</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>555051</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6961569</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128518190</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555113</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6961357</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>96790356</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6961448</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog, i stig</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>96790369</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555037</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6961430</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>yngre sandtallskog med tunt förnatäcke intill äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121310753</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>555048</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6961417</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121310742</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>555134</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6961338</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128154348</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strandåker, Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>555070</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6961372</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96790354</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>555101</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6961358</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog, i stig</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96790371</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>555037</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6961430</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>yngre sandtallskog med tunt förnatäcke intill äldre tallskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96790381</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dragsjömon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>554931</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6961560</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog med fina lavpartier</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121310741</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dragsjömoarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>555134</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6961338</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34529-2025 artfynd.xlsx
+++ b/artfynd/A 34529-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518185</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790367</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1228,6 +1253,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310745</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518182</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790366</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310749</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310759</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1864,6 +1919,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127623385</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369789</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518190</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2177,6 +2247,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790356</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2292,6 +2367,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790369</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2401,6 +2481,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310753</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2510,6 +2595,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2621,6 +2711,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128154348</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2737,6 +2832,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790354</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2853,6 +2953,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790371</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2967,6 +3072,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790381</t>
         </is>
       </c>
     </row>
@@ -3070,8 +3180,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310741</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>